--- a/2°Año/2°Semestre/ISO/Practicas/TP2/Ejercicio10.xlsx
+++ b/2°Año/2°Semestre/ISO/Practicas/TP2/Ejercicio10.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\elian\Desktop\Facultad-APU\2°Año\2°Semestre\ISO\Practicas\TP2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Elian\Desktop\Facultad\2°Año\2°Semestre\ISO\Practicas\TP2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E4D3A4F6-FEBF-445E-8CA8-BCA39FC3EAF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B69913E0-6B38-4F25-A2A2-6578C24E1344}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="15960" windowHeight="15585" xr2:uid="{7B701750-5A46-4DF5-AD5D-1373D66E98D5}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{7B701750-5A46-4DF5-AD5D-1373D66E98D5}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -20,23 +20,15 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="28">
   <si>
     <t>Proceso</t>
   </si>
@@ -111,13 +103,22 @@
   </si>
   <si>
     <t>r3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&gt;1 </t>
+  </si>
+  <si>
+    <t>6&lt;</t>
+  </si>
+  <si>
+    <t>5&lt;</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -206,6 +207,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -215,7 +217,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -551,26 +552,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF5F752E-FC80-4831-AC4C-0A3FC1229216}">
   <dimension ref="A1:AD31"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="3" width="9.7109375" customWidth="1"/>
+    <col min="1" max="3" width="9.75" customWidth="1"/>
     <col min="4" max="4" width="27" customWidth="1"/>
-    <col min="5" max="30" width="3.7109375" customWidth="1"/>
+    <col min="5" max="30" width="3.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:30">
+      <c r="A1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="4"/>
-    </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+      <c r="B1" s="5"/>
+    </row>
+    <row r="2" spans="1:30">
+      <c r="A2" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="6"/>
-    </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="B2" s="7"/>
+    </row>
+    <row r="3" spans="1:30">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -662,7 +663,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:30">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -672,11 +673,11 @@
       <c r="C4" s="1">
         <v>4</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="F4" s="1">
         <v>2</v>
@@ -685,15 +686,15 @@
         <v>16</v>
       </c>
       <c r="H4" s="1"/>
-      <c r="I4" s="1">
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1">
         <v>3</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="M4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
       <c r="P4" s="1"/>
@@ -712,7 +713,7 @@
       <c r="AC4" s="1"/>
       <c r="AD4" s="1"/>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:30">
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
@@ -722,7 +723,7 @@
       <c r="C5" s="1">
         <v>6</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E5" s="1"/>
@@ -760,7 +761,9 @@
       <c r="W5" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="X5" s="1"/>
+      <c r="X5" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="Y5" s="1"/>
       <c r="Z5" s="1"/>
       <c r="AA5" s="1"/>
@@ -768,7 +771,7 @@
       <c r="AC5" s="1"/>
       <c r="AD5" s="1"/>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:30">
       <c r="A6" s="1" t="s">
         <v>3</v>
       </c>
@@ -778,30 +781,30 @@
       <c r="C6" s="1">
         <v>4</v>
       </c>
-      <c r="D6" s="7"/>
+      <c r="D6" s="4"/>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
       <c r="H6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
+      <c r="I6" s="1">
+        <v>1</v>
+      </c>
+      <c r="J6" s="1">
+        <v>2</v>
+      </c>
       <c r="K6" s="1"/>
-      <c r="L6" s="1">
-        <v>1</v>
-      </c>
-      <c r="M6" s="1">
-        <v>2</v>
-      </c>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
       <c r="N6" s="1"/>
-      <c r="O6" s="1"/>
-      <c r="P6" s="1">
+      <c r="O6" s="1">
         <v>3</v>
       </c>
-      <c r="Q6" s="1" t="s">
+      <c r="P6" s="1" t="s">
         <v>22</v>
       </c>
+      <c r="Q6" s="1"/>
       <c r="R6" s="1"/>
       <c r="S6" s="1"/>
       <c r="T6" s="1"/>
@@ -816,7 +819,7 @@
       <c r="AC6" s="1"/>
       <c r="AD6" s="1"/>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:30">
       <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
@@ -826,7 +829,7 @@
       <c r="C7" s="1">
         <v>5</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E7" s="1"/>
@@ -834,33 +837,35 @@
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1" t="s">
+      <c r="J7" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="K7" s="1"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
       <c r="N7" s="1"/>
-      <c r="O7" s="1">
+      <c r="O7" s="1"/>
+      <c r="P7" s="1"/>
+      <c r="Q7" s="1">
         <v>1</v>
       </c>
-      <c r="P7" s="1" t="s">
+      <c r="R7" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="Q7" s="1" t="s">
+      <c r="S7" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="R7" s="1">
-        <v>2</v>
-      </c>
-      <c r="S7" s="1"/>
-      <c r="T7" s="1"/>
-      <c r="U7" s="1"/>
+      <c r="T7" s="1">
+        <v>3</v>
+      </c>
+      <c r="U7" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="V7" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W7" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="X7" s="1"/>
       <c r="Y7" s="1"/>
@@ -870,7 +875,7 @@
       <c r="AC7" s="1"/>
       <c r="AD7" s="1"/>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:30">
       <c r="A8" s="1" t="s">
         <v>10</v>
       </c>
@@ -880,7 +885,7 @@
       <c r="C8" s="1">
         <v>2</v>
       </c>
-      <c r="D8" s="7"/>
+      <c r="D8" s="4"/>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
@@ -896,13 +901,13 @@
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
-      <c r="R8" s="1"/>
-      <c r="S8" s="1">
+      <c r="R8" s="1">
         <v>1</v>
       </c>
-      <c r="T8" s="1" t="s">
+      <c r="S8" s="1" t="s">
         <v>23</v>
       </c>
+      <c r="T8" s="1"/>
       <c r="U8" s="1"/>
       <c r="V8" s="1"/>
       <c r="W8" s="1"/>
@@ -914,7 +919,7 @@
       <c r="AC8" s="1"/>
       <c r="AD8" s="1"/>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:30">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -928,45 +933,49 @@
         <v>2</v>
       </c>
       <c r="G9" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H9" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I9" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J9" s="3">
         <v>3</v>
       </c>
-      <c r="K9" s="3">
+      <c r="K9" s="4">
+        <v>4</v>
+      </c>
+      <c r="L9" s="3">
         <v>5</v>
       </c>
-      <c r="L9" s="3">
-        <v>2</v>
-      </c>
       <c r="M9" s="3">
+        <v>2</v>
+      </c>
+      <c r="N9" s="3">
         <v>4</v>
       </c>
-      <c r="N9" s="7"/>
-      <c r="O9" s="7"/>
-      <c r="P9" s="7"/>
-      <c r="Q9" s="7"/>
-      <c r="R9" s="7"/>
-      <c r="S9" s="7"/>
-      <c r="T9" s="7"/>
-      <c r="U9" s="7"/>
-      <c r="V9" s="7"/>
-      <c r="W9" s="7"/>
-      <c r="X9" s="7"/>
-      <c r="Y9" s="7"/>
-      <c r="Z9" s="7"/>
-      <c r="AA9" s="7"/>
-      <c r="AB9" s="7"/>
+      <c r="O9" s="4">
+        <v>2</v>
+      </c>
+      <c r="P9" s="4"/>
+      <c r="Q9" s="4"/>
+      <c r="R9" s="4"/>
+      <c r="S9" s="4"/>
+      <c r="T9" s="4"/>
+      <c r="U9" s="4"/>
+      <c r="V9" s="4"/>
+      <c r="W9" s="4"/>
+      <c r="X9" s="4"/>
+      <c r="Y9" s="4"/>
+      <c r="Z9" s="4"/>
+      <c r="AA9" s="4"/>
+      <c r="AB9" s="4"/>
       <c r="AC9" s="1"/>
       <c r="AD9" s="1"/>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:30">
       <c r="D10" s="1" t="s">
         <v>12</v>
       </c>
@@ -979,406 +988,43 @@
       <c r="G10" s="3">
         <v>4</v>
       </c>
-      <c r="H10" s="7">
-        <v>2</v>
-      </c>
-      <c r="I10" s="7">
-        <v>3</v>
-      </c>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="7"/>
-      <c r="M10" s="7"/>
-      <c r="N10" s="7"/>
-      <c r="O10" s="7"/>
-      <c r="P10" s="7"/>
-      <c r="Q10" s="7"/>
-      <c r="R10" s="7"/>
-      <c r="S10" s="7"/>
-      <c r="T10" s="7"/>
-      <c r="U10" s="7"/>
-      <c r="V10" s="7"/>
-      <c r="W10" s="7"/>
-      <c r="X10" s="7"/>
-      <c r="Y10" s="7"/>
-      <c r="Z10" s="7"/>
-      <c r="AA10" s="7"/>
-      <c r="AB10" s="7"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
+      <c r="M10" s="4"/>
+      <c r="N10" s="4"/>
+      <c r="O10" s="4"/>
+      <c r="P10" s="4"/>
+      <c r="Q10" s="4"/>
+      <c r="R10" s="4"/>
+      <c r="S10" s="4"/>
+      <c r="T10" s="4"/>
+      <c r="U10" s="4"/>
+      <c r="V10" s="4"/>
+      <c r="W10" s="4"/>
+      <c r="X10" s="4"/>
+      <c r="Y10" s="4"/>
+      <c r="Z10" s="4"/>
+      <c r="AA10" s="4"/>
+      <c r="AB10" s="4"/>
       <c r="AC10" s="1"/>
       <c r="AD10" s="1"/>
     </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" s="6"/>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E15" s="1">
-        <v>0</v>
-      </c>
-      <c r="F15" s="1">
-        <v>1</v>
-      </c>
-      <c r="G15" s="1">
-        <v>2</v>
-      </c>
-      <c r="H15" s="1">
-        <v>3</v>
-      </c>
-      <c r="I15" s="1">
-        <v>4</v>
-      </c>
-      <c r="J15" s="1">
-        <v>5</v>
-      </c>
-      <c r="K15" s="1">
-        <v>6</v>
-      </c>
-      <c r="L15" s="1">
-        <v>7</v>
-      </c>
-      <c r="M15" s="1">
-        <v>8</v>
-      </c>
-      <c r="N15" s="1">
-        <v>9</v>
-      </c>
-      <c r="O15" s="1">
-        <v>10</v>
-      </c>
-      <c r="P15" s="1">
-        <v>11</v>
-      </c>
-      <c r="Q15" s="1">
-        <v>12</v>
-      </c>
-      <c r="R15" s="1">
-        <v>13</v>
-      </c>
-      <c r="S15" s="1">
-        <v>14</v>
-      </c>
-      <c r="T15" s="1">
-        <v>15</v>
-      </c>
-      <c r="U15" s="1">
-        <v>16</v>
-      </c>
-      <c r="V15" s="1">
-        <v>17</v>
-      </c>
-      <c r="W15" s="1">
-        <v>18</v>
-      </c>
-      <c r="X15" s="1">
-        <v>19</v>
-      </c>
-      <c r="Y15" s="1">
-        <v>20</v>
-      </c>
-      <c r="Z15" s="1">
-        <v>21</v>
-      </c>
-      <c r="AA15" s="1">
-        <v>22</v>
-      </c>
-      <c r="AB15" s="1">
-        <v>23</v>
-      </c>
-      <c r="AC15" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD15" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B16" s="1">
-        <v>0</v>
-      </c>
-      <c r="C16" s="1">
-        <v>4</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1"/>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1"/>
-      <c r="P16" s="1"/>
-      <c r="Q16" s="1"/>
-      <c r="R16" s="1"/>
-      <c r="S16" s="1"/>
-      <c r="T16" s="1"/>
-      <c r="U16" s="1"/>
-      <c r="V16" s="1"/>
-      <c r="W16" s="1"/>
-      <c r="X16" s="1"/>
-      <c r="Y16" s="1"/>
-      <c r="Z16" s="1"/>
-      <c r="AA16" s="1"/>
-      <c r="AB16" s="1"/>
-      <c r="AC16" s="1"/>
-      <c r="AD16" s="1"/>
-    </row>
-    <row r="17" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B17" s="1">
-        <v>2</v>
-      </c>
-      <c r="C17" s="1">
-        <v>6</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
-      <c r="L17" s="1"/>
-      <c r="M17" s="1"/>
-      <c r="N17" s="1"/>
-      <c r="O17" s="1"/>
-      <c r="P17" s="1"/>
-      <c r="Q17" s="1"/>
-      <c r="R17" s="1"/>
-      <c r="S17" s="1"/>
-      <c r="T17" s="1"/>
-      <c r="U17" s="1"/>
-      <c r="V17" s="1"/>
-      <c r="W17" s="1"/>
-      <c r="X17" s="1"/>
-      <c r="Y17" s="1"/>
-      <c r="Z17" s="1"/>
-      <c r="AA17" s="1"/>
-      <c r="AB17" s="1"/>
-      <c r="AC17" s="1"/>
-      <c r="AD17" s="1"/>
-    </row>
-    <row r="18" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B18" s="1">
-        <v>3</v>
-      </c>
-      <c r="C18" s="1">
-        <v>4</v>
-      </c>
-      <c r="D18" s="7"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
-      <c r="M18" s="1"/>
-      <c r="N18" s="1"/>
-      <c r="O18" s="1"/>
-      <c r="P18" s="1"/>
-      <c r="Q18" s="1"/>
-      <c r="R18" s="1"/>
-      <c r="S18" s="1"/>
-      <c r="T18" s="1"/>
-      <c r="U18" s="1"/>
-      <c r="V18" s="1"/>
-      <c r="W18" s="1"/>
-      <c r="X18" s="1"/>
-      <c r="Y18" s="1"/>
-      <c r="Z18" s="1"/>
-      <c r="AA18" s="1"/>
-      <c r="AB18" s="1"/>
-      <c r="AC18" s="1"/>
-      <c r="AD18" s="1"/>
-    </row>
-    <row r="19" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B19" s="1">
-        <v>6</v>
-      </c>
-      <c r="C19" s="1">
-        <v>5</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
-      <c r="M19" s="1"/>
-      <c r="N19" s="1"/>
-      <c r="O19" s="1"/>
-      <c r="P19" s="1"/>
-      <c r="Q19" s="1"/>
-      <c r="R19" s="1"/>
-      <c r="S19" s="1"/>
-      <c r="T19" s="1"/>
-      <c r="U19" s="1"/>
-      <c r="V19" s="1"/>
-      <c r="W19" s="1"/>
-      <c r="X19" s="1"/>
-      <c r="Y19" s="1"/>
-      <c r="Z19" s="1"/>
-      <c r="AA19" s="1"/>
-      <c r="AB19" s="1"/>
-      <c r="AC19" s="1"/>
-      <c r="AD19" s="1"/>
-    </row>
-    <row r="20" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B20" s="1">
-        <v>8</v>
-      </c>
-      <c r="C20" s="1">
-        <v>2</v>
-      </c>
-      <c r="D20" s="7"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
-      <c r="L20" s="1"/>
-      <c r="M20" s="1"/>
-      <c r="N20" s="1"/>
-      <c r="O20" s="1"/>
-      <c r="P20" s="1"/>
-      <c r="Q20" s="1"/>
-      <c r="R20" s="1"/>
-      <c r="S20" s="1"/>
-      <c r="T20" s="1"/>
-      <c r="U20" s="1"/>
-      <c r="V20" s="1"/>
-      <c r="W20" s="1"/>
-      <c r="X20" s="1"/>
-      <c r="Y20" s="1"/>
-      <c r="Z20" s="1"/>
-      <c r="AA20" s="1"/>
-      <c r="AB20" s="1"/>
-      <c r="AC20" s="1"/>
-      <c r="AD20" s="1"/>
-    </row>
-    <row r="21" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
-      <c r="J21" s="7"/>
-      <c r="K21" s="7"/>
-      <c r="L21" s="7"/>
-      <c r="M21" s="7"/>
-      <c r="N21" s="7"/>
-      <c r="O21" s="7"/>
-      <c r="P21" s="7"/>
-      <c r="Q21" s="7"/>
-      <c r="R21" s="7"/>
-      <c r="S21" s="7"/>
-      <c r="T21" s="7"/>
-      <c r="U21" s="7"/>
-      <c r="V21" s="7"/>
-      <c r="W21" s="7"/>
-      <c r="X21" s="7"/>
-      <c r="Y21" s="7"/>
-      <c r="Z21" s="7"/>
-      <c r="AA21" s="7"/>
-      <c r="AB21" s="7"/>
-      <c r="AC21" s="7"/>
-      <c r="AD21" s="7"/>
-    </row>
-    <row r="22" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="D22" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="7"/>
-      <c r="J22" s="7"/>
-      <c r="K22" s="7"/>
-      <c r="L22" s="7"/>
-      <c r="M22" s="7"/>
-      <c r="N22" s="7"/>
-      <c r="O22" s="7"/>
-      <c r="P22" s="7"/>
-      <c r="Q22" s="7"/>
-      <c r="R22" s="7"/>
-      <c r="S22" s="7"/>
-      <c r="T22" s="7"/>
-      <c r="U22" s="7"/>
-      <c r="V22" s="7"/>
-      <c r="W22" s="7"/>
-      <c r="X22" s="7"/>
-      <c r="Y22" s="7"/>
-      <c r="Z22" s="7"/>
-      <c r="AA22" s="7"/>
-      <c r="AB22" s="7"/>
-      <c r="AC22" s="7"/>
-      <c r="AD22" s="7"/>
-    </row>
-    <row r="25" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="25" spans="8:8">
       <c r="H25" s="2"/>
     </row>
-    <row r="31" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="31" spans="8:8">
       <c r="H31" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="2">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A14:B14"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>